--- a/VerveStacks_MYS_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75841B23-F2E4-4A29-A362-3C06D3E7E9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC8FCBDD-7374-4385-8013-0B726DFA3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{66E76DAB-3E96-4481-BA79-C7D2A8A570F2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D28E554E-EE86-456B-B4C7-B047BC438E2A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1823,7 +1823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCBC0714-5033-48D2-BF8E-BEC3F53248CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF05917D-19CD-4535-8DE0-8F9D87B8F6EA}">
   <dimension ref="B3:L196"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MYS_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC8FCBDD-7374-4385-8013-0B726DFA3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{416C4BDA-8CE3-4279-B308-09C7A3B2DEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D28E554E-EE86-456B-B4C7-B047BC438E2A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D1555F7B-E10B-41F1-9BC6-F18126AFBBA3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1823,7 +1823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF05917D-19CD-4535-8DE0-8F9D87B8F6EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F55D592-A168-4B4C-BC72-D8BCB7039DB1}">
   <dimension ref="B3:L196"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
